--- a/Air Lease Corp LBO.xlsx
+++ b/Air Lease Corp LBO.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\OneDrive\Projects\Research\LBO\Air Release\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\GitHub\AirLease-LBO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA8E17E-2046-42A8-8AED-7BF048CED182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DAE749-7B47-46FC-BF3E-33AD28B28550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11676" yWindow="0" windowWidth="11460" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Context" sheetId="1" r:id="rId3"/>
+    <sheet name="LBO" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,25 +36,216 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Owner</author>
+  </authors>
+  <commentList>
+    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{021911C3-D2A6-4F19-84D4-B322A3254E76}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+"Air Lease stockholders will receive $65.00 in cash for each share of Class A common stock of Air Lease"</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{F225CD9C-940C-404D-BB81-9FF9F0C0F8FE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+The premium that investors will receive.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{AA3AA1B3-22D1-4150-99D3-043EF7E78994}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+First Press Release to annouce about the acquisition.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{DC5DAF06-380E-45A9-9BB0-C9ABE2E43076}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Closing Price of 29/8/2025. The 29 August 2025 closing price is used as it represents the unaffected share price prior to the 2 September 2025 press release.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{224AFEBB-2EAF-41D1-B526-ADD5435FB6DA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Q2 report is used since it reflects the financial before the press release date.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{5174199F-4000-4904-87A9-9BAE8421908B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Q2 10Q pg 7
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{F7EED158-1B70-4774-82CC-5E21F961A545}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Q2 10Q pg 7
+- Restricted Cash is excluded because it is not usable for debt repayment.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{F19BFD03-C854-484A-9AAC-775E3A40071C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+$7.4 billion total valuation </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>Link</t>
   </si>
   <si>
-    <t>Key Points</t>
-  </si>
-  <si>
-    <t>Air Lease Corporation Enters into Merger Agreement with Sumitomo Corporation, SMBC Aviation Capital, Apollo and Brookfield</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>- 09/2025, entered a definitive merger agreement to be acquired by a consortium through Sumisho Air Lease Corporation DAC
-- Transaction is expected to clise in the first half of 2026</t>
-  </si>
-  <si>
     <t>LBO</t>
   </si>
   <si>
@@ -74,35 +264,82 @@
     <t>Transaction Background</t>
   </si>
   <si>
-    <t>Vlauation at Entry</t>
-  </si>
-  <si>
     <t>Company Name</t>
   </si>
   <si>
     <t>Ticker</t>
   </si>
   <si>
-    <t>Lastest closing share price</t>
-  </si>
-  <si>
     <t>Air Lease</t>
   </si>
   <si>
     <t>AL</t>
   </si>
   <si>
-    <t>Date:</t>
-  </si>
-  <si>
-    <t>Lastest closing share price date</t>
+    <t>Close Share Price</t>
+  </si>
+  <si>
+    <t>Valuation at Entry</t>
+  </si>
+  <si>
+    <t>Offer value/share</t>
+  </si>
+  <si>
+    <t>% Premum /discount</t>
+  </si>
+  <si>
+    <t>Offer value (Equity Value)</t>
+  </si>
+  <si>
+    <t>Debt</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Enterprise Value</t>
+  </si>
+  <si>
+    <t>LTM EBITDA</t>
+  </si>
+  <si>
+    <t>Entry Multiple</t>
+  </si>
+  <si>
+    <t>Diluted shares outstanding</t>
+  </si>
+  <si>
+    <t>Minimum Cash</t>
+  </si>
+  <si>
+    <t>Exit Multiple</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1ZJsA_tjQNc</t>
+  </si>
+  <si>
+    <t>Transaction Financials and Assumptions (In thousands)</t>
+  </si>
+  <si>
+    <t>Capital Structure</t>
+  </si>
+  <si>
+    <t>Announcement Date</t>
+  </si>
+  <si>
+    <t>Assumed Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00_ ;\-[$$-409]#,##0.00\ "/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +381,45 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -170,7 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -208,22 +484,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -231,14 +500,32 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -524,148 +811,240 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D67666B-BBF3-42D3-9A9A-255DDFD17403}">
-  <dimension ref="B1:L15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D67666B-BBF3-42D3-9A9A-255DDFD17403}">
+  <dimension ref="B1:L25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
     <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B1" s="11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="12">
-        <v>46077</v>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="16">
+        <v>46023</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
     </row>
     <row r="5" spans="2:12" ht="7.05" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
+      <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
     </row>
     <row r="10" spans="2:12" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="H11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="H11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="13">
+        <v>65</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="10">
+        <f>K12/E15-1</f>
+        <v>9.0787044806175388E-2</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="13"/>
+        <v>27</v>
+      </c>
+      <c r="E14" s="12">
+        <v>45902</v>
+      </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="13">
+        <v>59.59</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="H16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="H18" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="15">
+        <v>20320406</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="15">
+        <v>454801</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="15">
+        <v>7400000</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="13"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="33.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="47.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="3" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="H22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H23" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C1" r:id="rId1" xr:uid="{04F446D4-B4A4-4BFE-A1B2-4241F3DAB186}"/>
+    <hyperlink ref="F15" r:id="rId1" xr:uid="{B5179E28-2C5B-45A6-B62B-402E313687AF}"/>
+    <hyperlink ref="L12" r:id="rId2" xr:uid="{B5DBADF4-CA8E-4820-A239-FBCCE60D6083}"/>
+    <hyperlink ref="F19" r:id="rId3" xr:uid="{209812A7-3F3E-4CB0-ABC6-55A1EDCBA0EE}"/>
+    <hyperlink ref="F20" r:id="rId4" xr:uid="{551CC1BF-FD9A-4757-81D4-B830F57EB88E}"/>
+    <hyperlink ref="F21" r:id="rId5" xr:uid="{2AB0C4A4-34FA-4307-89B4-421779F60B36}"/>
+    <hyperlink ref="C1" r:id="rId6" xr:uid="{B6F39D97-F455-4828-A00D-E7A581DD628F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
--- a/Air Lease Corp LBO.xlsx
+++ b/Air Lease Corp LBO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\GitHub\AirLease-LBO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DAE749-7B47-46FC-BF3E-33AD28B28550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7048B3C0-D9A8-4B85-8F66-E86885114C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11460" yWindow="0" windowWidth="11676" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Owner:</t>
         </r>
@@ -131,7 +131,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Closing Price of 29/8/2025. The 29 August 2025 closing price is used as it represents the unaffected share price prior to the 2 September 2025 press release.</t>
@@ -162,6 +162,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{E9109CA0-3D1B-4497-AE40-ED9968E7818E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- 10K Dec 2025 pg 73</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E19" authorId="0" shapeId="0" xr:uid="{5174199F-4000-4904-87A9-9BAE8421908B}">
       <text>
         <r>
@@ -182,7 +206,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Q2 10Q pg 7
+- 10K Dec 2025 pg 72
 </t>
         </r>
       </text>
@@ -207,7 +231,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-- Q2 10Q pg 7
+- 10K Dec 2025 pg 72
 - Restricted Cash is excluded because it is not usable for debt repayment.</t>
         </r>
       </text>
@@ -232,7 +256,155 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-$7.4 billion total valuation </t>
+Minimum cash is set at $454,801K, the full reported cash balance. This amount is already small compared to Air Lease's $33.3B in total assets, and the company relies on undrawn credit lines and commercial paper for liquidity rather than cash reserves. So none of the reported cash is treated as excess available to fund the deal.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="0" shapeId="0" xr:uid="{2739772C-82C3-4D62-AA2B-C3DEF6E14597}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+"SMBC, Citi, and Goldman Sachs Bank USA have provided $12.1 billion of committed financing in connection with the transaction."
+https://www.apollo.com/insights-news/pressreleases/2025/09/sumitomo-corporation--smbc-aviation-capital--apollo-and-brookfie</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{888E6FCF-8D0E-4451-BC78-99868FB3D32E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- SOFR + 1.10%, based on Air Lease's actual RCF/term loan spreads (10K Dec 2025  pg 55 - Unsecured term financings)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{6D110E95-783F-4F91-AC69-D34999F2813E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+market standard assumptions, not disclosed for this deal.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{1BFE9F56-0BB1-4E8E-8BC7-B73639E07F8F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+market standard assumptions, not disclosed for this deal.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{98192F6E-EAB2-434D-9024-9F868BC0209D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- 10K Dec 2025 pg 5 - Proposed Merger
+- 10K Dec 2025 pg 87 - Note 6. Stockholders’ Equity</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G28" authorId="0" shapeId="0" xr:uid="{A8061657-CC8B-41D5-9AE8-D8B8D64C3246}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- Series B: 4.650%
+- Series C: 4.125%
+- Series D: 6.000%</t>
         </r>
       </text>
     </comment>
@@ -241,7 +413,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t>Link</t>
   </si>
@@ -328,18 +500,60 @@
   </si>
   <si>
     <t>Assumed Date</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>xEBITDA</t>
+  </si>
+  <si>
+    <t>Interest(%)</t>
+  </si>
+  <si>
+    <t>Fees (%)</t>
+  </si>
+  <si>
+    <t>Fee ($)</t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Amortization</t>
+  </si>
+  <si>
+    <t>New acquisition term loan</t>
+  </si>
+  <si>
+    <t>Preferred stock (Series B/C/D, rolled)</t>
+  </si>
+  <si>
+    <t>Perpetual</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Sponsor common equity (plug)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="6">
+    <numFmt numFmtId="44" formatCode="_-&quot;XDR&quot;* #,##0.00_-;\-&quot;XDR&quot;* #,##0.00_-;_-&quot;XDR&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00_ ;\-[$$-409]#,##0.00\ "/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="182" formatCode="0.0000\x"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,19 +610,6 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -424,8 +625,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,8 +660,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -483,14 +699,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -516,13 +770,33 @@
     <xf numFmtId="43" fontId="5" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Currency" xfId="4" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="3" builtinId="5"/>
@@ -538,6 +812,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -812,12 +1090,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D67666B-BBF3-42D3-9A9A-255DDFD17403}">
-  <dimension ref="B1:L25"/>
+  <dimension ref="B1:L30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
     <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="6" max="8" width="12.77734375" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="11" width="12.77734375" customWidth="1"/>
+    <col min="12" max="12" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
@@ -939,9 +1222,7 @@
       <c r="E15" s="13">
         <v>59.59</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="F15" s="1"/>
       <c r="H15" s="8" t="s">
         <v>15</v>
       </c>
@@ -963,7 +1244,9 @@
       <c r="B18" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="14"/>
+      <c r="E18" s="15">
+        <v>3015749</v>
+      </c>
       <c r="H18" s="9" t="s">
         <v>16</v>
       </c>
@@ -973,7 +1256,7 @@
         <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>20320406</v>
+        <v>19730129</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>0</v>
@@ -987,7 +1270,7 @@
         <v>17</v>
       </c>
       <c r="E20" s="15">
-        <v>454801</v>
+        <v>466410</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>0</v>
@@ -998,11 +1281,10 @@
         <v>22</v>
       </c>
       <c r="E21" s="15">
-        <v>7400000</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>0</v>
-      </c>
+        <f>E20</f>
+        <v>466410</v>
+      </c>
+      <c r="F21" s="1"/>
       <c r="H21" s="8" t="s">
         <v>18</v>
       </c>
@@ -1035,16 +1317,130 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="E26" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="19">
+        <v>12100000000</v>
+      </c>
+      <c r="F27" s="29">
+        <f>E27/($E$18*1000)</f>
+        <v>4.0122702519340967</v>
+      </c>
+      <c r="G27" s="20">
+        <f>3.66%+(1%+1.15%+0.1%*2)/2</f>
+        <v>4.8350000000000004E-2</v>
+      </c>
+      <c r="H27" s="20">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="I27" s="18">
+        <f>E27*H27</f>
+        <v>133099999.99999999</v>
+      </c>
+      <c r="J27" s="21">
+        <v>5</v>
+      </c>
+      <c r="K27" s="23">
+        <f>I27/J27</f>
+        <v>26619999.999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="19">
+        <v>900000</v>
+      </c>
+      <c r="F28" s="29">
+        <f>E28/($E$18*1000)</f>
+        <v>2.9843332452402372E-4</v>
+      </c>
+      <c r="G28" s="20">
+        <f xml:space="preserve"> (4.65% + 4.125% + 6%)/3</f>
+        <v>4.9249999999999995E-2</v>
+      </c>
+      <c r="H28" s="20">
+        <v>0</v>
+      </c>
+      <c r="I28" s="18">
+        <f>E28*H28</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="19">
+        <v>16068</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="24"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="28">
+        <f>SUM(E27:E28)</f>
+        <v>12100900000</v>
+      </c>
+      <c r="F30" s="28">
+        <f>SUM(F27:F28)</f>
+        <v>4.0125686852586204</v>
+      </c>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="27"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F15" r:id="rId1" xr:uid="{B5179E28-2C5B-45A6-B62B-402E313687AF}"/>
-    <hyperlink ref="L12" r:id="rId2" xr:uid="{B5DBADF4-CA8E-4820-A239-FBCCE60D6083}"/>
-    <hyperlink ref="F19" r:id="rId3" xr:uid="{209812A7-3F3E-4CB0-ABC6-55A1EDCBA0EE}"/>
-    <hyperlink ref="F20" r:id="rId4" xr:uid="{551CC1BF-FD9A-4757-81D4-B830F57EB88E}"/>
-    <hyperlink ref="F21" r:id="rId5" xr:uid="{2AB0C4A4-34FA-4307-89B4-421779F60B36}"/>
-    <hyperlink ref="C1" r:id="rId6" xr:uid="{B6F39D97-F455-4828-A00D-E7A581DD628F}"/>
+    <hyperlink ref="F19" r:id="rId1" xr:uid="{209812A7-3F3E-4CB0-ABC6-55A1EDCBA0EE}"/>
+    <hyperlink ref="C1" r:id="rId2" xr:uid="{B6F39D97-F455-4828-A00D-E7A581DD628F}"/>
+    <hyperlink ref="L12" r:id="rId3" xr:uid="{68BB1722-524B-4964-B50F-11119179AACB}"/>
+    <hyperlink ref="F20" r:id="rId4" xr:uid="{11C99AC4-BB9A-4A5C-9D01-AD3D01125F73}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId7"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
--- a/Air Lease Corp LBO.xlsx
+++ b/Air Lease Corp LBO.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\GitHub\AirLease-LBO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7048B3C0-D9A8-4B85-8F66-E86885114C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EED2113-E30D-4DDE-8074-56CC01E83846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="0" windowWidth="11676" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11460" yWindow="0" windowWidth="11676" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="2" r:id="rId1"/>
     <sheet name="LBO" sheetId="3" r:id="rId2"/>
+    <sheet name="Shares" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -182,7 +183,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-- 10K Dec 2025 pg 73</t>
+- EBITDA = Revenue - Selling, general and administrative - Stock-based compensation expense (10K Dec 2025 pg 73)</t>
         </r>
       </text>
     </comment>
@@ -413,7 +414,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
   <si>
     <t>Link</t>
   </si>
@@ -538,7 +539,82 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Sponsor common equity (plug)</t>
+    <t>Diluted Share Count Calculation</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Full Diluted Shares</t>
+  </si>
+  <si>
+    <t>Offer price</t>
+  </si>
+  <si>
+    <t>Basic shares outstanding (lastest filling)</t>
+  </si>
+  <si>
+    <t>In-the-money exercisable options</t>
+  </si>
+  <si>
+    <t>Total proceeds</t>
+  </si>
+  <si>
+    <t>Total shares repurchased</t>
+  </si>
+  <si>
+    <t>Net dilutive options</t>
+  </si>
+  <si>
+    <t>Dilutive impact of shares from other securities</t>
+  </si>
+  <si>
+    <t>Settled stock based comp</t>
+  </si>
+  <si>
+    <t>Net diluted shares outstanding</t>
+  </si>
+  <si>
+    <t>Options outstanding</t>
+  </si>
+  <si>
+    <t>Tranche 1</t>
+  </si>
+  <si>
+    <t>Tranche 2</t>
+  </si>
+  <si>
+    <t>Tranche 3</t>
+  </si>
+  <si>
+    <t>Tranche 4</t>
+  </si>
+  <si>
+    <t>Tranche 5</t>
+  </si>
+  <si>
+    <t>Tranche 6</t>
+  </si>
+  <si>
+    <t>Tranche 7</t>
+  </si>
+  <si>
+    <t>Tranche 8</t>
+  </si>
+  <si>
+    <t>Tranche 9</t>
+  </si>
+  <si>
+    <t>Tranche 10</t>
+  </si>
+  <si>
+    <t>Outstanding</t>
+  </si>
+  <si>
+    <t>Exercise Price</t>
+  </si>
+  <si>
+    <t>Dilutuve Shares</t>
   </si>
 </sst>
 </file>
@@ -550,10 +626,10 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00_ ;\-[$$-409]#,##0.00\ "/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    <numFmt numFmtId="182" formatCode="0.0000\x"/>
+    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="167" formatCode="0.0000\x"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -634,8 +710,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -666,8 +763,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -736,6 +845,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -744,7 +877,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -777,8 +910,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -791,8 +924,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -812,10 +956,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1090,13 +1230,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D67666B-BBF3-42D3-9A9A-255DDFD17403}">
-  <dimension ref="B1:L30"/>
+  <dimension ref="B1:L29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
     <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
     <col min="6" max="8" width="12.77734375" customWidth="1"/>
     <col min="9" max="9" width="15.88671875" customWidth="1"/>
     <col min="10" max="11" width="12.77734375" customWidth="1"/>
@@ -1245,7 +1385,8 @@
         <v>19</v>
       </c>
       <c r="E18" s="15">
-        <v>3015749</v>
+        <f>3015749-219443-48930</f>
+        <v>2747376</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>16</v>
@@ -1349,7 +1490,7 @@
       </c>
       <c r="F27" s="29">
         <f>E27/($E$18*1000)</f>
-        <v>4.0122702519340967</v>
+        <v>4.4042024098630836</v>
       </c>
       <c r="G27" s="20">
         <f>3.66%+(1%+1.15%+0.1%*2)/2</f>
@@ -1379,7 +1520,7 @@
       </c>
       <c r="F28" s="29">
         <f>E28/($E$18*1000)</f>
-        <v>2.9843332452402372E-4</v>
+        <v>3.2758530321295667E-4</v>
       </c>
       <c r="G28" s="20">
         <f xml:space="preserve"> (4.65% + 4.125% + 6%)/3</f>
@@ -1400,38 +1541,27 @@
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="19">
-        <v>16068</v>
-      </c>
-      <c r="F29" s="29"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="24"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B30" s="25" t="s">
+      <c r="B29" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="28">
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="28">
         <f>SUM(E27:E28)</f>
         <v>12100900000</v>
       </c>
-      <c r="F30" s="28">
+      <c r="F29" s="30">
         <f>SUM(F27:F28)</f>
-        <v>4.0125686852586204</v>
-      </c>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="27"/>
+        <v>4.4045299951662962</v>
+      </c>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="28">
+        <f>SUM(I27:I28)</f>
+        <v>133099999.99999999</v>
+      </c>
+      <c r="J29" s="26"/>
+      <c r="K29" s="27"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1443,4 +1573,198 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{305532C0-5839-49D5-A277-5B700563CFFB}">
+  <dimension ref="A2:F32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="15.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="B2" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="35"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="38"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="38"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="38"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="38"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C20" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Air Lease Corp LBO.xlsx
+++ b/Air Lease Corp LBO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\GitHub\AirLease-LBO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EED2113-E30D-4DDE-8074-56CC01E83846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15B6519-E26A-4877-B82E-2BE5D436C310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="0" windowWidth="11676" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="372" windowWidth="15000" windowHeight="11868" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="2" r:id="rId1"/>
@@ -139,7 +139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{224AFEBB-2EAF-41D1-B526-ADD5435FB6DA}">
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{224AFEBB-2EAF-41D1-B526-ADD5435FB6DA}">
       <text>
         <r>
           <rPr>
@@ -163,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{E9109CA0-3D1B-4497-AE40-ED9968E7818E}">
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{E9109CA0-3D1B-4497-AE40-ED9968E7818E}">
       <text>
         <r>
           <rPr>
@@ -187,7 +187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{5174199F-4000-4904-87A9-9BAE8421908B}">
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{5174199F-4000-4904-87A9-9BAE8421908B}">
       <text>
         <r>
           <rPr>
@@ -212,7 +212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{F7EED158-1B70-4774-82CC-5E21F961A545}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{F7EED158-1B70-4774-82CC-5E21F961A545}">
       <text>
         <r>
           <rPr>
@@ -237,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{F19BFD03-C854-484A-9AAC-775E3A40071C}">
+    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{F19BFD03-C854-484A-9AAC-775E3A40071C}">
       <text>
         <r>
           <rPr>
@@ -406,6 +406,137 @@
 - Series B: 4.650%
 - Series C: 4.125%
 - Series D: 6.000%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H37" authorId="0" shapeId="0" xr:uid="{12E39372-0232-4BA4-B6E0-6C39D34A2930}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Not disclosed. Estimated at 1.0% of TEV using the Lehman Formula since Air Lease is a large transaction of around $28.2bn.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Owner</author>
+  </authors>
+  <commentList>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{CA03F46C-BBE3-4AB7-BD6B-324D263C1159}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+10-K Dec 2025 p39</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{DF4BCF68-F330-4C56-8931-A0D9DB3D88BB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Note 11 (Earnings Per Share) confirms  RSUs are the only dilutive instrument, 10-K Dec 2025 p96.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{6862413F-E34B-4452-8106-330CDA493B9F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+- 10-K Dec 2025 p97 (unvested RSUs). 
+- Since there is no disclosure on how equity awards will be treated at close, full acceleration is assumed as standard merger treatment.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{9C959944-629C-4255-AC6F-CE809316FA36}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+No stock options, warrants, or convertible securities. Note 11 (Earnings Per Share) confirms diluted EPS reflects only RSU dilution, using the treasury stock method, 10-K Dec 2025 p96</t>
         </r>
       </text>
     </comment>
@@ -414,7 +545,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="79">
   <si>
     <t>Link</t>
   </si>
@@ -461,24 +592,15 @@
     <t>% Premum /discount</t>
   </si>
   <si>
-    <t>Offer value (Equity Value)</t>
-  </si>
-  <si>
     <t>Debt</t>
   </si>
   <si>
     <t>Cash</t>
   </si>
   <si>
-    <t>Enterprise Value</t>
-  </si>
-  <si>
     <t>LTM EBITDA</t>
   </si>
   <si>
-    <t>Entry Multiple</t>
-  </si>
-  <si>
     <t>Diluted shares outstanding</t>
   </si>
   <si>
@@ -494,9 +616,6 @@
     <t>Transaction Financials and Assumptions (In thousands)</t>
   </si>
   <si>
-    <t>Capital Structure</t>
-  </si>
-  <si>
     <t>Announcement Date</t>
   </si>
   <si>
@@ -515,9 +634,6 @@
     <t>Fees (%)</t>
   </si>
   <si>
-    <t>Fee ($)</t>
-  </si>
-  <si>
     <t>Term</t>
   </si>
   <si>
@@ -615,6 +731,57 @@
   </si>
   <si>
     <t>Dilutuve Shares</t>
+  </si>
+  <si>
+    <t>Offer value (In thousands)</t>
+  </si>
+  <si>
+    <t>Debt (In thousands)</t>
+  </si>
+  <si>
+    <t>Cash (In thousands)</t>
+  </si>
+  <si>
+    <t>Enterprise Value (In thousands)</t>
+  </si>
+  <si>
+    <t>LTM EBITDA (In thousands)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry Multiple </t>
+  </si>
+  <si>
+    <t>Sources and Uses</t>
+  </si>
+  <si>
+    <t>Sponsor equity</t>
+  </si>
+  <si>
+    <t>% Capital</t>
+  </si>
+  <si>
+    <t>Debt refinancing</t>
+  </si>
+  <si>
+    <t>Financing fees</t>
+  </si>
+  <si>
+    <t>Equity payment</t>
+  </si>
+  <si>
+    <t>Sources (In thousands)</t>
+  </si>
+  <si>
+    <t>Uses  (In thousands)</t>
+  </si>
+  <si>
+    <t>Capital Structure (In thousands)</t>
+  </si>
+  <si>
+    <t>Transaction fees</t>
+  </si>
+  <si>
+    <t>Fees</t>
   </si>
 </sst>
 </file>
@@ -629,7 +796,7 @@
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     <numFmt numFmtId="167" formatCode="0.0000\x"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -731,8 +898,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -772,6 +953,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -877,7 +1064,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -900,9 +1087,6 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -921,22 +1105,52 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1230,36 +1444,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D67666B-BBF3-42D3-9A9A-255DDFD17403}">
-  <dimension ref="B1:L29"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="8" width="12.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
     <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="11" width="12.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" customWidth="1"/>
     <col min="12" max="12" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="16">
+      <c r="C2" s="15">
         <v>46023</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
@@ -1274,18 +1494,21 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="2:12" ht="7.05" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="7.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
       <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
@@ -1300,8 +1523,8 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="2:12" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>6</v>
       </c>
@@ -1315,7 +1538,7 @@
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>7</v>
       </c>
@@ -1332,7 +1555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -1347,15 +1570,15 @@
         <v>9.0787044806175388E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E14" s="12">
         <v>45902</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>11</v>
       </c>
@@ -1364,89 +1587,116 @@
       </c>
       <c r="F15" s="1"/>
       <c r="H15" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="K15" s="55">
+        <f>K12*K16/1000</f>
+        <v>7371589.5499999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="15">
+        <v>18</v>
+      </c>
+      <c r="K16" s="39">
+        <f>Shares!E16</f>
+        <v>113409070</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="H18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K18" s="40">
+        <f>E20</f>
+        <v>19730129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="41">
         <f>3015749-219443-48930</f>
         <v>2747376</v>
       </c>
-      <c r="H18" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="15">
+      <c r="H19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="40">
+        <f>E21</f>
+        <v>466410</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="41">
         <v>19730129</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="15">
-        <v>466410</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="15">
-        <f>E20</f>
+        <v>16</v>
+      </c>
+      <c r="E21" s="41">
         <v>466410</v>
       </c>
-      <c r="F21" s="1"/>
+      <c r="F21" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="H21" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+      <c r="K21" s="56">
+        <f>K15+K18-K19</f>
+        <v>26635308.550000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="14"/>
+        <v>19</v>
+      </c>
+      <c r="E22" s="41">
+        <v>454801</v>
+      </c>
+      <c r="F22" s="1"/>
       <c r="H22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+      <c r="K22" s="40">
+        <f>E19</f>
+        <v>2747376</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="42">
+        <v>9.6948173639137796</v>
+      </c>
       <c r="H23" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+      <c r="K23" s="57">
+        <f>K21/K22</f>
+        <v>9.6948173639137849</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -1458,117 +1708,308 @@
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="E26" s="17" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E26" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="J26" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="K26" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G26" s="17" t="s">
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="K26" s="17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="19">
-        <v>12100000000</v>
-      </c>
-      <c r="F27" s="29">
-        <f>E27/($E$18*1000)</f>
+      <c r="E27" s="18">
+        <f>12100000000/1000</f>
+        <v>12100000</v>
+      </c>
+      <c r="F27" s="24">
+        <f>E27/$E$19</f>
         <v>4.4042024098630836</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="19">
         <f>3.66%+(1%+1.15%+0.1%*2)/2</f>
         <v>4.8350000000000004E-2</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="19">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="17">
         <f>E27*H27</f>
-        <v>133099999.99999999</v>
-      </c>
-      <c r="J27" s="21">
+        <v>133100</v>
+      </c>
+      <c r="J27" s="20">
         <v>5</v>
       </c>
-      <c r="K27" s="23">
+      <c r="K27" s="22">
         <f>I27/J27</f>
-        <v>26619999.999999996</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+        <v>26620</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="19">
+        <v>32</v>
+      </c>
+      <c r="E28" s="18">
+        <f>900000</f>
         <v>900000</v>
       </c>
-      <c r="F28" s="29">
-        <f>E28/($E$18*1000)</f>
-        <v>3.2758530321295667E-4</v>
-      </c>
-      <c r="G28" s="20">
+      <c r="F28" s="24">
+        <f>E28/$E$19</f>
+        <v>0.32758530321295665</v>
+      </c>
+      <c r="G28" s="19">
         <f xml:space="preserve"> (4.65% + 4.125% + 6%)/3</f>
         <v>4.9249999999999995E-2</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="19">
         <v>0</v>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="17">
         <f>E28*H28</f>
         <v>0</v>
       </c>
-      <c r="J28" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" s="24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B29" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="28">
+      <c r="J28" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="52">
         <f>SUM(E27:E28)</f>
-        <v>12100900000</v>
-      </c>
-      <c r="F29" s="30">
+        <v>13000000</v>
+      </c>
+      <c r="F29" s="53">
         <f>SUM(F27:F28)</f>
-        <v>4.4045299951662962</v>
-      </c>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="28">
+        <v>4.7317877130760406</v>
+      </c>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="52">
         <f>SUM(I27:I28)</f>
-        <v>133099999.99999999</v>
-      </c>
-      <c r="J29" s="26"/>
-      <c r="K29" s="27"/>
+        <v>133100</v>
+      </c>
+      <c r="J29" s="51"/>
+      <c r="K29" s="54"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="H33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D34" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" t="str">
+        <f>B27</f>
+        <v>New acquisition term loan</v>
+      </c>
+      <c r="D35" s="40">
+        <f>E27</f>
+        <v>12100000</v>
+      </c>
+      <c r="E35" s="44">
+        <f>F27</f>
+        <v>4.4042024098630836</v>
+      </c>
+      <c r="F35" s="10">
+        <f>D35/$D$40</f>
+        <v>0.43973106767460951</v>
+      </c>
+      <c r="H35" t="s">
+        <v>73</v>
+      </c>
+      <c r="I35" s="40">
+        <f>K15</f>
+        <v>7371589.5499999998</v>
+      </c>
+      <c r="J35" s="24">
+        <f>I35/$E$19</f>
+        <v>2.6831382198869029</v>
+      </c>
+      <c r="K35" s="10">
+        <f>I35/$I$40</f>
+        <v>0.26789396225458628</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="35">
+        <f>D40-D35</f>
+        <v>15416818.550000001</v>
+      </c>
+      <c r="E36" s="24">
+        <f>D36/$E$19</f>
+        <v>5.6114701992009834</v>
+      </c>
+      <c r="F36" s="10">
+        <f>D36/$D$40</f>
+        <v>0.56026893232539055</v>
+      </c>
+      <c r="H36" t="s">
+        <v>71</v>
+      </c>
+      <c r="I36" s="40">
+        <f>K18</f>
+        <v>19730129</v>
+      </c>
+      <c r="J36" s="24">
+        <f t="shared" ref="J36:J38" si="0">I36/$E$19</f>
+        <v>7.1814447676619437</v>
+      </c>
+      <c r="K36" s="10">
+        <f>I36/$I$40</f>
+        <v>0.717020718225436</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H37" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="43">
+        <f>1%*28.2*1000000</f>
+        <v>282000</v>
+      </c>
+      <c r="J37" s="24">
+        <f t="shared" si="0"/>
+        <v>0.10264339500672642</v>
+      </c>
+      <c r="K37" s="10">
+        <f>I37/$I$40</f>
+        <v>1.0248277775557015E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H38" t="s">
+        <v>72</v>
+      </c>
+      <c r="I38" s="40">
+        <f>I29</f>
+        <v>133100</v>
+      </c>
+      <c r="J38" s="24">
+        <f t="shared" si="0"/>
+        <v>4.8446226508493923E-2</v>
+      </c>
+      <c r="K38" s="10">
+        <f>I38/$I$40</f>
+        <v>4.8370417444207042E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B40" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="46"/>
+      <c r="D40" s="47">
+        <f>I40</f>
+        <v>27516818.550000001</v>
+      </c>
+      <c r="E40" s="48">
+        <f>SUM(E35:E36)</f>
+        <v>10.015672609064067</v>
+      </c>
+      <c r="F40" s="49">
+        <f>SUM(F35:F36)</f>
+        <v>1</v>
+      </c>
+      <c r="H40" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" s="47">
+        <f>SUM(I35:I38)</f>
+        <v>27516818.550000001</v>
+      </c>
+      <c r="J40" s="48">
+        <f>SUM(J35:J38)</f>
+        <v>10.015672609064067</v>
+      </c>
+      <c r="K40" s="49">
+        <f>SUM(K35:K38)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F19" r:id="rId1" xr:uid="{209812A7-3F3E-4CB0-ABC6-55A1EDCBA0EE}"/>
+    <hyperlink ref="F20" r:id="rId1" xr:uid="{209812A7-3F3E-4CB0-ABC6-55A1EDCBA0EE}"/>
     <hyperlink ref="C1" r:id="rId2" xr:uid="{B6F39D97-F455-4828-A00D-E7A581DD628F}"/>
     <hyperlink ref="L12" r:id="rId3" xr:uid="{68BB1722-524B-4964-B50F-11119179AACB}"/>
-    <hyperlink ref="F20" r:id="rId4" xr:uid="{11C99AC4-BB9A-4A5C-9D01-AD3D01125F73}"/>
+    <hyperlink ref="F21" r:id="rId4" xr:uid="{11C99AC4-BB9A-4A5C-9D01-AD3D01125F73}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId5"/>
@@ -1576,8 +2017,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{305532C0-5839-49D5-A277-5B700563CFFB}">
-  <dimension ref="A2:F32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{305532C0-5839-49D5-A277-5B700563CFFB}">
+  <dimension ref="A2:E32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.88671875" bestFit="1" customWidth="1"/>
@@ -1585,186 +2026,265 @@
     <col min="3" max="5" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="B2" s="31" t="s">
+    <row r="2" spans="1:5" s="26" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="B2" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="34">
+        <f>LBO!K12</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="14">
+        <v>112035408</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="E8" s="36">
+        <f>C21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="E9" s="36">
+        <f>SUMPRODUCT(D21:D30,E21:E30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="35"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="35"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="E10" s="36">
+        <f>IF(E9&lt;&gt;0,E6/E9,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="38"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="E11" s="36">
+        <f>E8-E10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="38"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="E12" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E13" s="36"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+      <c r="E14" s="14">
+        <f>1373662</f>
+        <v>1373662</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E15" s="36"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="38"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="38"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="8" t="s">
-        <v>52</v>
+      <c r="E16" s="38">
+        <f>E7+E14</f>
+        <v>113409070</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
+        <v>37</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C20" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>66</v>
+      <c r="C20" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
+        <v>49</v>
+      </c>
+      <c r="C21" s="31">
+        <v>0</v>
+      </c>
+      <c r="D21" s="31">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <f>IF(D21&lt;$E$6,C21)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
+        <v>50</v>
+      </c>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22">
+        <f t="shared" ref="E22:E30" si="0">IF(D22&lt;$E$6,C22)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
+        <v>52</v>
+      </c>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
+        <v>53</v>
+      </c>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
+        <v>54</v>
+      </c>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
+        <v>55</v>
+      </c>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
+        <v>56</v>
+      </c>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
+        <v>57</v>
+      </c>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
+        <v>58</v>
+      </c>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
+        <v>37</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>